--- a/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
+++ b/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/trans/SYVbT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/varun_agarwal_wri_org/Documents/EPS India 2.0/EPS 2023/EPS India Update-2023-24/Completed EPS Variables/trans/SYVbT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{9263B2CC-E985-4409-9A4B-45893CE32F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B64170C6-052C-40DD-A11B-0B4940232EB9}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="13_ncr:1_{9263B2CC-E985-4409-9A4B-45893CE32F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D26D8073-6046-44EE-A161-8FAD6DF70EAE}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="172">
   <si>
     <t>SYVbT Start Year Vehicles by Technology</t>
   </si>
@@ -689,21 +689,24 @@
   <si>
     <t>https://iess2047.gov.in/_/theme/documents/IESS2047_Version_3.0.xlsx</t>
   </si>
+  <si>
+    <t>jeeps</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="###0.00_)"/>
-    <numFmt numFmtId="166" formatCode="#,##0_)"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="#,##0_);\(#,##0\);&quot;-&quot;_);@"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="###0.00_)"/>
+    <numFmt numFmtId="168" formatCode="#,##0_)"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0_);\(#,##0\);&quot;-&quot;_);@"/>
+    <numFmt numFmtId="171" formatCode="0.00000"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
   </numFmts>
   <fonts count="53">
     <font>
@@ -1771,7 +1774,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment horizontal="left"/>
@@ -1806,28 +1809,28 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="6">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="6">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="6">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1916,7 +1919,7 @@
     <xf numFmtId="49" fontId="19" fillId="0" borderId="6">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyNumberFormat="0">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyNumberFormat="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
@@ -1953,11 +1956,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1969,19 +1972,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="140" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="142" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="142" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1991,11 +1999,17 @@
     <xf numFmtId="0" fontId="41" fillId="29" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="29" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="29" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="29" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="142" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
@@ -2004,62 +2018,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="140" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="29" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="29" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="32" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="32" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="32" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="32" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2078,13 +2101,13 @@
     <xf numFmtId="0" fontId="49" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="32" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="32" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2096,27 +2119,30 @@
     <xf numFmtId="0" fontId="49" fillId="32" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="48" fillId="33" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="48" fillId="33" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="33" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="33" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="33" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="33" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="140"/>
     <xf numFmtId="0" fontId="51" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2124,14 +2150,14 @@
     <xf numFmtId="9" fontId="51" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="51" fillId="34" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="51" fillId="34" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="172" fontId="51" fillId="34" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="52" fillId="34" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2155,29 +2181,57 @@
     <xf numFmtId="2" fontId="7" fillId="34" borderId="0" xfId="73" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="43" fillId="0" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="43" fillId="0" borderId="0" xfId="141" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="32" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2189,29 +2243,14 @@
     <xf numFmtId="0" fontId="49" fillId="32" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="144">
@@ -2383,8 +2422,8 @@
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>4027</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1166077</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>116545</xdr:rowOff>
     </xdr:to>
@@ -2991,80 +3030,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="73.140625" customWidth="1"/>
+    <col min="2" max="2" width="73.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" s="32"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="B4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="B5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="B6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:7">
+      <c r="B7" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
+    <row r="9" spans="1:7" s="10" customFormat="1">
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:7">
       <c r="B11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:7">
       <c r="B12" s="3">
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:7">
       <c r="B13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:7">
       <c r="B14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:7">
       <c r="B15" t="s">
         <v>109</v>
       </c>
@@ -3089,8 +3131,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="30">
-      <c r="B21" s="25" t="s">
+    <row r="21" spans="2:2" ht="29">
+      <c r="B21" s="31" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3120,7 +3162,7 @@
       </c>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="86" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3135,12 +3177,12 @@
       </c>
     </row>
     <row r="32" spans="2:2">
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="9" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3233,11 +3275,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -3249,7 +3291,7 @@
       <c r="A2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="73">
+      <c r="B2" s="84">
         <f>F18+O18</f>
         <v>101</v>
       </c>
@@ -3261,7 +3303,7 @@
       <c r="A3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="84">
         <f>R18-B2</f>
         <v>1200</v>
       </c>
@@ -3270,412 +3312,415 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="6" spans="1:18" ht="15.75">
-      <c r="A6" s="34"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="38"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.75">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40" t="s">
+    <row r="5" spans="1:18" ht="15" thickBot="1"/>
+    <row r="6" spans="1:18" ht="15.5">
+      <c r="A6" s="43"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="47"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.5">
+      <c r="A7" s="48"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="41" t="s">
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="42"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75">
-      <c r="A8" s="39"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="46"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40" t="s">
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="51"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.5">
+      <c r="A8" s="48"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="56"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.5">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="41" t="s">
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="42"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="51"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="39"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47" t="s">
+      <c r="A10" s="48"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="48" t="s">
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="49"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="59"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51" t="s">
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="53" t="s">
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="54"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="64"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="109" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="108" t="s">
+      <c r="C12" s="112" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="109"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="109"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="108" t="s">
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="L12" s="109"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="109"/>
-      <c r="O12" s="109"/>
-      <c r="P12" s="109"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="94" t="s">
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="113"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="114"/>
+      <c r="R12" s="115" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="103"/>
-      <c r="B13" s="106"/>
-      <c r="C13" s="97" t="s">
+      <c r="A13" s="107"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="97" t="s">
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="119"/>
+      <c r="J13" s="120"/>
+      <c r="K13" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="98"/>
-      <c r="O13" s="98"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="95"/>
-    </row>
-    <row r="14" spans="1:18" ht="25.5">
-      <c r="A14" s="103"/>
-      <c r="B14" s="106"/>
-      <c r="C14" s="100" t="s">
+      <c r="L13" s="119"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="120"/>
+      <c r="R13" s="116"/>
+    </row>
+    <row r="14" spans="1:18" ht="26">
+      <c r="A14" s="107"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="121" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="100" t="s">
+      <c r="D14" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="124" t="s">
         <v>123</v>
       </c>
-      <c r="G14" s="100" t="s">
+      <c r="G14" s="121" t="s">
         <v>124</v>
       </c>
-      <c r="H14" s="100" t="s">
+      <c r="H14" s="121" t="s">
         <v>125</v>
       </c>
-      <c r="I14" s="100" t="s">
+      <c r="I14" s="121" t="s">
         <v>126</v>
       </c>
-      <c r="J14" s="55" t="s">
+      <c r="J14" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="K14" s="100" t="s">
+      <c r="K14" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="L14" s="100" t="s">
+      <c r="L14" s="124" t="s">
         <v>128</v>
       </c>
-      <c r="M14" s="100" t="s">
+      <c r="M14" s="124" t="s">
         <v>129</v>
       </c>
-      <c r="N14" s="100" t="s">
+      <c r="N14" s="121" t="s">
         <v>130</v>
       </c>
-      <c r="O14" s="100" t="s">
+      <c r="O14" s="124" t="s">
         <v>131</v>
       </c>
-      <c r="P14" s="56" t="s">
+      <c r="P14" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="Q14" s="57" t="s">
+      <c r="Q14" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="R14" s="95"/>
+      <c r="R14" s="116"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="103"/>
-      <c r="B15" s="106"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="101"/>
-      <c r="N15" s="101"/>
-      <c r="O15" s="101"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="95"/>
+      <c r="A15" s="107"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="116"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="104"/>
-      <c r="B16" s="107"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102"/>
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="102"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="96"/>
+      <c r="A16" s="108"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="126"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="126"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="117"/>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="63">
+      <c r="A17" s="73">
         <v>1</v>
       </c>
-      <c r="B17" s="64">
+      <c r="B17" s="74">
         <v>2</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="75">
         <v>3</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="76">
         <v>4</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="76">
         <v>5</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="76">
         <v>6</v>
       </c>
-      <c r="G17" s="65">
+      <c r="G17" s="75">
         <v>7</v>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="75">
         <v>8</v>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="75">
         <v>9</v>
       </c>
-      <c r="J17" s="66">
+      <c r="J17" s="77">
         <v>10</v>
       </c>
-      <c r="K17" s="65">
+      <c r="K17" s="75">
         <v>11</v>
       </c>
-      <c r="L17" s="65">
+      <c r="L17" s="76">
         <v>12</v>
       </c>
-      <c r="M17" s="65">
+      <c r="M17" s="76">
         <v>13</v>
       </c>
-      <c r="N17" s="65">
+      <c r="N17" s="75">
         <v>14</v>
       </c>
-      <c r="O17" s="65">
+      <c r="O17" s="76">
         <v>15</v>
       </c>
-      <c r="P17" s="65">
+      <c r="P17" s="75">
         <v>16</v>
       </c>
-      <c r="Q17" s="66">
+      <c r="Q17" s="77">
         <v>17</v>
       </c>
-      <c r="R17" s="67">
+      <c r="R17" s="78">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="68">
+      <c r="A18" s="79">
         <v>2016</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="70">
+      <c r="C18" s="81">
         <v>586</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="81">
         <v>37</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="81">
         <v>22</v>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="81">
         <v>96</v>
       </c>
-      <c r="G18" s="70">
+      <c r="G18" s="81">
         <v>100</v>
       </c>
-      <c r="H18" s="70">
+      <c r="H18" s="81">
         <v>57</v>
       </c>
-      <c r="I18" s="70" t="s">
+      <c r="I18" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="J18" s="71">
+      <c r="J18" s="82">
         <f>SUM(C18:I18)</f>
         <v>898</v>
       </c>
-      <c r="K18" s="70">
+      <c r="K18" s="81">
         <v>155</v>
       </c>
-      <c r="L18" s="70">
+      <c r="L18" s="81">
         <v>85</v>
       </c>
-      <c r="M18" s="70">
+      <c r="M18" s="81">
         <v>128</v>
       </c>
-      <c r="N18" s="70">
+      <c r="N18" s="81">
         <v>30</v>
       </c>
-      <c r="O18" s="70">
+      <c r="O18" s="81">
         <v>5</v>
       </c>
-      <c r="P18" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="70">
+      <c r="P18" s="81">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="81">
         <f>SUM(K18:P18)</f>
         <v>403</v>
       </c>
-      <c r="R18" s="72">
+      <c r="R18" s="83">
         <f>(J18+Q18)</f>
         <v>1301</v>
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="C20" s="73"/>
-      <c r="J20" s="73"/>
+      <c r="C20" s="84"/>
+      <c r="J20" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="L14:L16"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="C12:J12"/>
@@ -3692,9 +3737,6 @@
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="L14:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3704,9 +3746,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3720,7 +3762,7 @@
         <v>97</v>
       </c>
       <c r="B2">
-        <v>620</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3752,7 +3794,7 @@
       </c>
       <c r="B12">
         <f>'India AVLo'!B4</f>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -3776,7 +3818,7 @@
       </c>
       <c r="B16">
         <f>B5/B12</f>
-        <v>679677.41935483867</v>
+        <v>678976.54034544982</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3794,7 +3836,7 @@
       </c>
       <c r="B20" s="6">
         <f>B2*(B16/SUM(B16:B17))</f>
-        <v>528.86184647366849</v>
+        <v>574.83678221684181</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3803,9 +3845,9 @@
       </c>
       <c r="B21" s="6">
         <f>B2*(B17/SUM(B16:B17))</f>
-        <v>91.138153526331578</v>
-      </c>
-      <c r="D21" s="9"/>
+        <v>99.163217783158174</v>
+      </c>
+      <c r="D21" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3815,16 +3857,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:R53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="16.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="15" width="10.42578125" customWidth="1"/>
+    <col min="6" max="9" width="16.7265625" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" customWidth="1"/>
+    <col min="12" max="12" width="17.1796875" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" customWidth="1"/>
+    <col min="14" max="15" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="8:18">
@@ -3838,110 +3880,110 @@
       <c r="P1" s="4"/>
     </row>
     <row r="2" spans="8:18">
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="8:18">
-      <c r="K3" s="82" t="s">
+      <c r="K3" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="82" t="s">
+      <c r="L3" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="82" t="s">
+      <c r="M3" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83">
+      <c r="N3" s="94"/>
+      <c r="O3" s="94">
         <v>2021</v>
       </c>
-      <c r="P3" s="84">
+      <c r="P3" s="95">
         <v>2020</v>
       </c>
-      <c r="Q3" s="84">
+      <c r="Q3" s="95">
         <v>2022</v>
       </c>
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="8:18">
-      <c r="K4" s="76" t="s">
+      <c r="K4" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="76" t="s">
+      <c r="L4" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="77" t="s">
+      <c r="M4" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85">
+      <c r="N4" s="96"/>
+      <c r="O4" s="96">
         <f>AVERAGE(P4,Q4)</f>
         <v>104.74412535343794</v>
       </c>
-      <c r="P4" s="86">
+      <c r="P4" s="97">
         <v>112.33148104789421</v>
       </c>
-      <c r="Q4" s="86">
+      <c r="Q4" s="97">
         <v>97.156769658981673</v>
       </c>
     </row>
     <row r="5" spans="8:18">
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="77" t="s">
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85">
+      <c r="N5" s="96"/>
+      <c r="O5" s="96">
         <f t="shared" ref="O5:O22" si="0">AVERAGE(P5,Q5)</f>
         <v>2.0377197166191792</v>
       </c>
-      <c r="P5" s="86">
+      <c r="P5" s="97">
         <v>1.8296891955271379</v>
       </c>
-      <c r="Q5" s="86">
+      <c r="Q5" s="97">
         <v>2.2457502377112206</v>
       </c>
     </row>
     <row r="6" spans="8:18">
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="77" t="s">
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85">
+      <c r="N6" s="96"/>
+      <c r="O6" s="96">
         <f t="shared" si="0"/>
         <v>0.92532263866839159</v>
       </c>
-      <c r="P6" s="86">
+      <c r="P6" s="97">
         <v>0.19440447702475838</v>
       </c>
-      <c r="Q6" s="86">
+      <c r="Q6" s="97">
         <v>1.6562408003120248</v>
       </c>
     </row>
     <row r="7" spans="8:18">
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="77" t="s">
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85">
+      <c r="N7" s="96"/>
+      <c r="O7" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P7" s="86">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="86">
+      <c r="P7" s="97">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="97">
         <v>0</v>
       </c>
     </row>
@@ -3952,22 +3994,22 @@
       <c r="I8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76" t="s">
+      <c r="K8" s="87"/>
+      <c r="L8" s="87" t="s">
         <v>161</v>
       </c>
-      <c r="M8" s="77" t="s">
+      <c r="M8" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="N8" s="85"/>
-      <c r="O8" s="85">
+      <c r="N8" s="96"/>
+      <c r="O8" s="96">
         <f t="shared" si="0"/>
         <v>11.252819894556255</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="97">
         <v>11.982278595144958</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="97">
         <v>10.523361193967553</v>
       </c>
     </row>
@@ -3975,26 +4017,26 @@
       <c r="H9">
         <v>1632594</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="77" t="s">
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85">
+      <c r="N9" s="96"/>
+      <c r="O9" s="96">
         <f t="shared" si="0"/>
         <v>0.21700054907896946</v>
       </c>
-      <c r="P9" s="86">
+      <c r="P9" s="97">
         <v>0.19483379829503997</v>
       </c>
-      <c r="Q9" s="86">
+      <c r="Q9" s="97">
         <v>0.23916729986289895</v>
       </c>
     </row>
@@ -4002,28 +4044,28 @@
       <c r="H10">
         <v>5826471</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="28" t="s">
         <v>69</v>
       </c>
       <c r="J10" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="76"/>
-      <c r="L10" s="76" t="s">
+      <c r="K10" s="87"/>
+      <c r="L10" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="77" t="s">
+      <c r="M10" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85">
+      <c r="N10" s="96"/>
+      <c r="O10" s="96">
         <f t="shared" si="0"/>
         <v>284.06234460149028</v>
       </c>
-      <c r="P10" s="86">
+      <c r="P10" s="97">
         <v>303.59966407909599</v>
       </c>
-      <c r="Q10" s="86">
+      <c r="Q10" s="97">
         <v>264.52502512388457</v>
       </c>
     </row>
@@ -4031,26 +4073,26 @@
       <c r="H11">
         <v>6829196</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="28" t="s">
         <v>70</v>
       </c>
       <c r="J11" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="77" t="s">
+      <c r="K11" s="87"/>
+      <c r="L11" s="87"/>
+      <c r="M11" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85">
+      <c r="N11" s="96"/>
+      <c r="O11" s="96">
         <f t="shared" si="0"/>
         <v>6.7071769119231872</v>
       </c>
-      <c r="P11" s="86">
+      <c r="P11" s="97">
         <v>6.2289631530384897</v>
       </c>
-      <c r="Q11" s="86">
+      <c r="Q11" s="97">
         <v>7.1853906708078847</v>
       </c>
     </row>
@@ -4058,135 +4100,135 @@
       <c r="H12">
         <v>1817717</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="28" t="s">
         <v>71</v>
       </c>
       <c r="J12" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="77" t="s">
+      <c r="K12" s="87"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="N12" s="85"/>
-      <c r="O12" s="85">
+      <c r="N12" s="96"/>
+      <c r="O12" s="96">
         <f t="shared" si="0"/>
         <v>3.5299488209865602</v>
       </c>
-      <c r="P12" s="86">
+      <c r="P12" s="97">
         <v>1.6195304197900073</v>
       </c>
-      <c r="Q12" s="86">
+      <c r="Q12" s="97">
         <v>5.440367222183113</v>
       </c>
     </row>
     <row r="13" spans="8:18">
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="77" t="s">
+      <c r="K13" s="87"/>
+      <c r="L13" s="87"/>
+      <c r="M13" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="N13" s="85"/>
-      <c r="O13" s="85">
+      <c r="N13" s="96"/>
+      <c r="O13" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="86">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="86">
+      <c r="P13" s="97">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="97">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="8:18">
-      <c r="I14" s="23" t="s">
+      <c r="I14" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="88" t="s">
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="99" t="s">
         <v>162</v>
       </c>
-      <c r="N14" s="89"/>
-      <c r="O14" s="85">
+      <c r="N14" s="100"/>
+      <c r="O14" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="90">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="90">
+      <c r="P14" s="101">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="101">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="8:18">
-      <c r="I15" s="23" t="s">
+      <c r="I15" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76" t="s">
+      <c r="K15" s="87"/>
+      <c r="L15" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="M15" s="77" t="s">
+      <c r="M15" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85">
+      <c r="N15" s="96"/>
+      <c r="O15" s="96">
         <f t="shared" si="0"/>
         <v>980.75769960136677</v>
       </c>
-      <c r="P15" s="86">
+      <c r="P15" s="97">
         <v>1056.5782761040491</v>
       </c>
-      <c r="Q15" s="86">
+      <c r="Q15" s="97">
         <v>904.93712309868454</v>
       </c>
     </row>
     <row r="16" spans="8:18">
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="77" t="s">
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="N16" s="85"/>
-      <c r="O16" s="85">
+      <c r="N16" s="96"/>
+      <c r="O16" s="96">
         <f t="shared" si="0"/>
         <v>30.008640551160532</v>
       </c>
-      <c r="P16" s="86">
+      <c r="P16" s="97">
         <v>9.5955645660307187</v>
       </c>
-      <c r="Q16" s="86">
+      <c r="Q16" s="97">
         <v>50.421716536290347</v>
       </c>
     </row>
     <row r="17" spans="8:17">
-      <c r="I17" s="23" t="s">
+      <c r="I17" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76" t="s">
+      <c r="K17" s="87"/>
+      <c r="L17" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="77" t="s">
+      <c r="M17" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85">
+      <c r="N17" s="96"/>
+      <c r="O17" s="96">
         <f t="shared" si="0"/>
         <v>170.32435090852658</v>
       </c>
-      <c r="P17" s="86">
+      <c r="P17" s="97">
         <v>186.11609283155451</v>
       </c>
-      <c r="Q17" s="86">
+      <c r="Q17" s="97">
         <v>154.53260898549865</v>
       </c>
     </row>
@@ -4194,91 +4236,91 @@
       <c r="H18">
         <v>1723423</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="28" t="s">
         <v>72</v>
       </c>
       <c r="J18" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="77" t="s">
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="N18" s="85"/>
-      <c r="O18" s="85">
+      <c r="N18" s="96"/>
+      <c r="O18" s="96">
         <f t="shared" si="0"/>
         <v>40.782362600960042</v>
       </c>
-      <c r="P18" s="86">
+      <c r="P18" s="97">
         <v>43.819154446090913</v>
       </c>
-      <c r="Q18" s="86">
+      <c r="Q18" s="97">
         <v>37.745570755829178</v>
       </c>
     </row>
     <row r="19" spans="8:17">
-      <c r="I19" s="23" t="s">
+      <c r="I19" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="77" t="s">
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="N19" s="85"/>
-      <c r="O19" s="85">
+      <c r="N19" s="96"/>
+      <c r="O19" s="96">
         <f t="shared" si="0"/>
         <v>5.1108518527659692</v>
       </c>
-      <c r="P19" s="86">
+      <c r="P19" s="97">
         <v>0.69188138599090909</v>
       </c>
-      <c r="Q19" s="86">
+      <c r="Q19" s="97">
         <v>9.5298223195410294</v>
       </c>
     </row>
     <row r="20" spans="8:17">
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76" t="s">
+      <c r="K20" s="87"/>
+      <c r="L20" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="M20" s="77" t="s">
+      <c r="M20" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="N20" s="85"/>
-      <c r="O20" s="85">
+      <c r="N20" s="96"/>
+      <c r="O20" s="96">
         <f t="shared" si="0"/>
         <v>82.801942761484483</v>
       </c>
-      <c r="P20" s="86">
+      <c r="P20" s="97">
         <v>89.801520396853277</v>
       </c>
-      <c r="Q20" s="86">
+      <c r="Q20" s="97">
         <v>75.802365126115689</v>
       </c>
     </row>
     <row r="21" spans="8:17">
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="77" t="s">
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="N21" s="85"/>
-      <c r="O21" s="85">
+      <c r="N21" s="96"/>
+      <c r="O21" s="96">
         <f t="shared" si="0"/>
         <v>3.5168945969112677</v>
       </c>
-      <c r="P21" s="86">
+      <c r="P21" s="97">
         <v>3.7468038133661534</v>
       </c>
-      <c r="Q21" s="86">
+      <c r="Q21" s="97">
         <v>3.2869853804563816</v>
       </c>
     </row>
@@ -4286,96 +4328,97 @@
       <c r="H22">
         <v>3458917</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="28" t="s">
         <v>151</v>
       </c>
       <c r="J22" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="77" t="s">
+      <c r="K22" s="87"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="N22" s="85"/>
-      <c r="O22" s="85">
+      <c r="N22" s="96"/>
+      <c r="O22" s="96">
         <f t="shared" si="0"/>
         <v>0.85648543246402853</v>
       </c>
-      <c r="P22" s="86">
+      <c r="P22" s="97">
         <v>0.12177112393439997</v>
       </c>
-      <c r="Q22" s="86">
+      <c r="Q22" s="97">
         <v>1.5911997409936571</v>
       </c>
     </row>
     <row r="23" spans="8:17">
-      <c r="I23" s="23" t="s">
+      <c r="I23" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="92"/>
-      <c r="P23" s="27"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="105"/>
     </row>
     <row r="24" spans="8:17">
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="92"/>
-      <c r="P24" s="27"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="105"/>
     </row>
     <row r="25" spans="8:17">
       <c r="H25">
         <v>8202990</v>
       </c>
-      <c r="I25" s="23" t="s">
+      <c r="I25" s="28" t="s">
         <v>71</v>
       </c>
       <c r="J25" t="s">
         <v>80</v>
       </c>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="92"/>
-      <c r="O25" s="92"/>
-      <c r="P25" s="27"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="105"/>
     </row>
     <row r="26" spans="8:17">
       <c r="H26">
         <v>54372</v>
       </c>
-      <c r="I26" s="23" t="s">
+      <c r="I26" s="28" t="s">
         <v>77</v>
       </c>
       <c r="J26" t="s">
         <v>85</v>
       </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="92"/>
-      <c r="O26" s="92"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="104"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="10"/>
     </row>
     <row r="27" spans="8:17">
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="28" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="28" spans="8:17">
-      <c r="I28" s="23" t="s">
+      <c r="I28" s="28" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="8:17">
-      <c r="I29" s="23" t="s">
+      <c r="I29" s="28" t="s">
         <v>76</v>
       </c>
       <c r="K29" s="2" t="s">
@@ -4388,25 +4431,25 @@
       <c r="P29" s="4"/>
     </row>
     <row r="30" spans="8:17">
-      <c r="I30" s="23" t="s">
+      <c r="I30" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K30" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="L30" s="16" t="s">
+      <c r="L30" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M30" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="20">
         <v>2007</v>
       </c>
       <c r="O30" s="1">
         <v>2021</v>
       </c>
-      <c r="P30" s="18">
+      <c r="P30" s="21">
         <v>2020</v>
       </c>
       <c r="Q30" s="1">
@@ -4417,30 +4460,30 @@
       <c r="H31">
         <v>243682349</v>
       </c>
-      <c r="I31" s="23" t="s">
+      <c r="I31" s="28" t="s">
         <v>77</v>
       </c>
       <c r="J31" t="s">
         <v>86</v>
       </c>
-      <c r="K31" s="76" t="s">
+      <c r="K31" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="L31" s="76" t="s">
+      <c r="L31" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="M31" s="77" t="s">
+      <c r="M31" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="N31" s="78"/>
-      <c r="O31" s="81">
+      <c r="N31" s="89"/>
+      <c r="O31" s="92">
         <f t="shared" ref="O31:O36" si="1">AVERAGE(P31,Q31)</f>
         <v>275.00462735910941</v>
       </c>
-      <c r="P31" s="79">
+      <c r="P31" s="90">
         <v>272.50350329668049</v>
       </c>
-      <c r="Q31" s="79">
+      <c r="Q31" s="90">
         <v>277.50575142153832</v>
       </c>
     </row>
@@ -4448,47 +4491,53 @@
       <c r="H32">
         <v>37729158</v>
       </c>
-      <c r="I32" s="23" t="s">
+      <c r="I32" s="28" t="s">
         <v>73</v>
       </c>
       <c r="J32" t="s">
         <v>87</v>
       </c>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
-      <c r="M32" s="80" t="s">
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="91" t="s">
         <v>157</v>
       </c>
-      <c r="N32" s="78"/>
-      <c r="O32" s="81">
+      <c r="N32" s="89"/>
+      <c r="O32" s="92">
         <f t="shared" si="1"/>
         <v>2.1713300531385471</v>
       </c>
-      <c r="P32" s="79">
+      <c r="P32" s="90">
         <v>0.9651836008146889</v>
       </c>
-      <c r="Q32" s="79">
+      <c r="Q32" s="90">
         <v>3.3774765054624054</v>
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="I33" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="80" t="s">
+      <c r="H33">
+        <v>2462112</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s">
+        <v>171</v>
+      </c>
+      <c r="K33" s="87"/>
+      <c r="L33" s="87"/>
+      <c r="M33" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="N33" s="78"/>
-      <c r="O33" s="81">
+      <c r="N33" s="89"/>
+      <c r="O33" s="92">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P33" s="79">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="79">
+      <c r="P33" s="90">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="90">
         <v>0</v>
       </c>
     </row>
@@ -4496,85 +4545,85 @@
       <c r="H34">
         <v>471815</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="28" t="s">
         <v>72</v>
       </c>
       <c r="J34" t="s">
         <v>88</v>
       </c>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76" t="s">
+      <c r="K34" s="87"/>
+      <c r="L34" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="80" t="s">
+      <c r="M34" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="N34" s="78"/>
-      <c r="O34" s="81">
+      <c r="N34" s="89"/>
+      <c r="O34" s="92">
         <f t="shared" si="1"/>
         <v>171.1175232012468</v>
       </c>
-      <c r="P34" s="79">
+      <c r="P34" s="90">
         <v>169.70198722559434</v>
       </c>
-      <c r="Q34" s="79">
+      <c r="Q34" s="90">
         <v>172.53305917689926</v>
       </c>
     </row>
     <row r="35" spans="1:17">
-      <c r="I35" s="23" t="s">
+      <c r="I35" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K35" s="76"/>
-      <c r="L35" s="76"/>
-      <c r="M35" s="80" t="s">
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="N35" s="78"/>
-      <c r="O35" s="81">
+      <c r="N35" s="89"/>
+      <c r="O35" s="92">
         <f t="shared" si="1"/>
         <v>5.1470583168784421</v>
       </c>
-      <c r="P35" s="79">
+      <c r="P35" s="90">
         <v>3.4633058617468238</v>
       </c>
-      <c r="Q35" s="79">
+      <c r="Q35" s="90">
         <v>6.8308107720100599</v>
       </c>
     </row>
     <row r="36" spans="1:17">
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K36" s="76"/>
-      <c r="L36" s="76"/>
-      <c r="M36" s="80" t="s">
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="N36" s="78"/>
-      <c r="O36" s="81">
+      <c r="N36" s="89"/>
+      <c r="O36" s="92">
         <f t="shared" si="1"/>
         <v>1.3220924074858182</v>
       </c>
-      <c r="P36" s="79">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="79">
+      <c r="P36" s="90">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="90">
         <v>2.6441848149716365</v>
       </c>
     </row>
     <row r="37" spans="1:17">
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="28" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="28" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="I39" s="23" t="s">
+      <c r="I39" s="28" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4583,10 +4632,10 @@
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:17">
-      <c r="K41" s="3" t="s">
+      <c r="K41" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="L41" s="23" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4604,12 +4653,12 @@
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="28">
+      <c r="K42" s="24"/>
+      <c r="L42" s="36">
         <f>J44</f>
         <v>0</v>
       </c>
-      <c r="M42" s="28"/>
+      <c r="M42" s="36"/>
     </row>
     <row r="43" spans="1:17">
       <c r="B43" s="1" t="s">
@@ -4618,27 +4667,27 @@
       <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28">
+      <c r="K43" s="36"/>
+      <c r="L43" s="36">
         <f>K43</f>
         <v>0</v>
       </c>
-      <c r="M43" s="28"/>
+      <c r="M43" s="36"/>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="1" t="s">
@@ -4646,7 +4695,7 @@
       </c>
       <c r="B44">
         <f>SUMIFS($H$9:$H$39,$I$9:$I$39,"Psgr LDV")</f>
-        <v>37729158</v>
+        <v>40191270</v>
       </c>
       <c r="C44">
         <f>SUMIFS($H$9:$H$39,$I$9:$I$39,"Frgt LDV")</f>
@@ -4655,28 +4704,28 @@
       <c r="E44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="24">
         <f>O12/SUM(O10:O14)</f>
         <v>1.1994411056790654E-2</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="24">
         <f>O11/SUM(O10:O14)</f>
         <v>2.2790312548990003E-2</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="24">
         <f>O10/SUM(O10:O14)</f>
         <v>0.96521527639421945</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19">
-        <v>0</v>
-      </c>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28">
+      <c r="I44" s="24"/>
+      <c r="J44" s="24">
+        <v>0</v>
+      </c>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36">
         <f>K44</f>
         <v>0</v>
       </c>
-      <c r="M44" s="28"/>
+      <c r="M44" s="36"/>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="1" t="s">
@@ -4693,27 +4742,27 @@
       <c r="E45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="24">
         <f>O6/SUM(O4:O9)</f>
         <v>7.7642727259177027E-3</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="24">
         <f>(O5+O9)/SUM(O4:O9)</f>
         <v>1.8919090846763319E-2</v>
       </c>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19">
+      <c r="H45" s="24"/>
+      <c r="I45" s="24">
         <f>(O4+O8)/SUM(O4:O9)</f>
         <v>0.97331663642731892</v>
       </c>
-      <c r="J45" s="19">
-        <v>0</v>
-      </c>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19">
-        <v>0</v>
-      </c>
-      <c r="M45" s="28"/>
+      <c r="J45" s="24">
+        <v>0</v>
+      </c>
+      <c r="K45" s="24"/>
+      <c r="L45" s="24">
+        <v>0</v>
+      </c>
+      <c r="M45" s="36"/>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="1" t="s">
@@ -4730,22 +4779,22 @@
       <c r="E46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="24">
         <f>O16/SUM(O15:O16)</f>
         <v>2.9688998692449682E-2</v>
       </c>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19">
+      <c r="G46" s="24"/>
+      <c r="H46" s="24">
         <f>O15/SUM(O15,O16)</f>
         <v>0.97031100130755032</v>
       </c>
-      <c r="I46" s="19">
-        <v>0</v>
-      </c>
-      <c r="J46" s="19">
-        <v>0</v>
-      </c>
-      <c r="M46" s="28"/>
+      <c r="I46" s="24">
+        <v>0</v>
+      </c>
+      <c r="J46" s="24">
+        <v>0</v>
+      </c>
+      <c r="M46" s="36"/>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="1" t="s">
@@ -4758,34 +4807,34 @@
       <c r="E47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="24">
         <f>O22/SUM(O20:O22)</f>
         <v>9.8248610391590066E-3</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="24">
         <f>O21/SUM(O20:O22)</f>
         <v>4.0342776881349379E-2</v>
       </c>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19">
+      <c r="H47" s="24"/>
+      <c r="I47" s="24">
         <f>O20/SUM(O20:O22)</f>
         <v>0.94983236207949162</v>
       </c>
-      <c r="J47" s="19">
+      <c r="J47" s="24">
         <v>0</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
-      <c r="M47" s="28"/>
+      <c r="M47" s="36"/>
     </row>
     <row r="48" spans="1:17">
-      <c r="K48" s="3" t="s">
+      <c r="K48" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="L48" s="3" t="s">
+      <c r="L48" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="M48" s="28"/>
+      <c r="M48" s="36"/>
     </row>
     <row r="49" spans="5:13">
       <c r="E49" s="2" t="s">
@@ -4796,60 +4845,60 @@
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28">
+      <c r="K49" s="36"/>
+      <c r="L49" s="36">
         <f>K49</f>
         <v>0</v>
       </c>
-      <c r="M49" s="28"/>
+      <c r="M49" s="36"/>
     </row>
     <row r="50" spans="5:13">
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28">
+      <c r="K50" s="36"/>
+      <c r="L50" s="36">
         <f>K50</f>
         <v>0</v>
       </c>
-      <c r="M50" s="28"/>
+      <c r="M50" s="36"/>
     </row>
     <row r="51" spans="5:13">
       <c r="E51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F51" s="19">
+      <c r="F51" s="24">
         <f>O36/(SUM(O34:O36))</f>
         <v>7.4447726186911249E-3</v>
       </c>
-      <c r="G51" s="19">
+      <c r="G51" s="24">
         <f>O35/(SUM(O34:O36))</f>
         <v>2.8983358959887292E-2</v>
       </c>
-      <c r="H51" s="19">
-        <v>0</v>
-      </c>
-      <c r="I51" s="19">
+      <c r="H51" s="24">
+        <v>0</v>
+      </c>
+      <c r="I51" s="24">
         <f>O34/(SUM(O34:O36))</f>
         <v>0.96357186842142162</v>
       </c>
-      <c r="J51" s="19">
-        <v>0</v>
-      </c>
-      <c r="K51" s="19"/>
-      <c r="L51" s="28">
+      <c r="J51" s="24">
+        <v>0</v>
+      </c>
+      <c r="K51" s="24"/>
+      <c r="L51" s="36">
         <f>J53</f>
         <v>0</v>
       </c>
@@ -4858,20 +4907,20 @@
       <c r="E52" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="19">
+      <c r="F52" s="24">
         <f>O33/SUM(O31:O33)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="24">
         <f>O32/SUM(O31:O33)</f>
         <v>7.8337604509798632E-3</v>
       </c>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19">
+      <c r="H52" s="24"/>
+      <c r="I52" s="24">
         <f>O31/SUM(O31:O33)</f>
         <v>0.99216623954902017</v>
       </c>
-      <c r="J52" s="19">
+      <c r="J52" s="24">
         <v>0</v>
       </c>
     </row>
@@ -4883,18 +4932,18 @@
         <f>O19/(SUM(O17:O19))</f>
         <v>2.3637542325496121E-2</v>
       </c>
-      <c r="G53" s="19">
+      <c r="G53" s="24">
         <f>O18/SUM(O17:O19)</f>
         <v>0.18861725009544417</v>
       </c>
-      <c r="H53" s="19">
+      <c r="H53" s="24">
         <f>O17/SUM(O17:O19)</f>
         <v>0.78774520757905986</v>
       </c>
-      <c r="I53" s="19">
-        <v>0</v>
-      </c>
-      <c r="J53" s="19">
+      <c r="I53" s="24">
+        <v>0</v>
+      </c>
+      <c r="J53" s="24">
         <v>0</v>
       </c>
     </row>
@@ -4908,13 +4957,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4975,12 +5024,12 @@
       <c r="B8">
         <v>74744</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
@@ -4989,16 +5038,16 @@
       <c r="B9">
         <v>318896</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="21">
         <v>2021</v>
       </c>
       <c r="I9" s="1">
@@ -5009,16 +5058,16 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="34">
         <f>AVERAGE(I10,J10)</f>
         <v>0.34499999999999997</v>
       </c>
@@ -5034,16 +5083,16 @@
         <v>51</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="34">
         <f>AVERAGE(I11,J11)</f>
         <v>0.65</v>
       </c>
@@ -5058,16 +5107,16 @@
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="34">
         <v>0.1</v>
       </c>
     </row>
@@ -5075,19 +5124,19 @@
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="25">
         <v>10</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="34">
         <v>0.3</v>
       </c>
     </row>
@@ -5095,12 +5144,12 @@
       <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="25">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="42" t="s">
         <v>106</v>
       </c>
       <c r="G15" s="6">
@@ -5109,11 +5158,11 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="E16" s="33" t="s">
+      <c r="B16" s="26"/>
+      <c r="E16" s="42" t="s">
         <v>105</v>
       </c>
       <c r="G16" s="6">
@@ -5126,6 +5175,7 @@
       <c r="A17" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
@@ -5135,7 +5185,7 @@
         <f>B8/B13</f>
         <v>7474.4</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="42" t="s">
         <v>107</v>
       </c>
       <c r="G18" s="6">
@@ -5151,7 +5201,7 @@
         <f>B9/B14</f>
         <v>6377.92</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="42" t="s">
         <v>108</v>
       </c>
       <c r="G19" s="6">
@@ -5194,14 +5244,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:3" ht="29">
+      <c r="A1" s="30" t="s">
         <v>93</v>
       </c>
       <c r="B1" t="s">
@@ -5215,19 +5265,19 @@
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="27">
-        <v>3</v>
+      <c r="B2" s="35">
+        <v>3.18</v>
       </c>
       <c r="C2">
         <v>1.7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="C3">
         <v>6.0999999999999979</v>
@@ -5238,14 +5288,14 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="C4">
         <v>17.34</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="32" t="s">
         <v>11</v>
       </c>
       <c r="B5">
@@ -5256,13 +5306,13 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="27">
-        <v>3</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="35">
+        <v>2.6</v>
+      </c>
+      <c r="C6" s="35">
         <v>1974.4736422180429</v>
       </c>
     </row>
@@ -5271,10 +5321,10 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5288,20 +5338,20 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="19.26953125" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10" ht="29">
+      <c r="A1" s="30" t="s">
         <v>89</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -5332,15 +5382,15 @@
       </c>
       <c r="B2" s="6">
         <f>'India Road'!$B44*'India Road'!F44</f>
-        <v>452539.02987860155</v>
+        <v>482070.6132744585</v>
       </c>
       <c r="C2" s="6">
         <f>'India Road'!$B44*'India Road'!G44</f>
-        <v>859859.30303022661</v>
+        <v>915971.60504084546</v>
       </c>
       <c r="D2" s="6">
         <f>'India Road'!$B44*'India Road'!H44</f>
-        <v>36416759.667091176</v>
+        <v>38793227.781684697</v>
       </c>
       <c r="E2" s="6">
         <f>'India Road'!$B44*'India Road'!I44</f>
@@ -5398,26 +5448,26 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="B4" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
         <f>'India Aircraft'!B20</f>
-        <v>528.86184647366849</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
+        <v>574.83678221684181</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
         <v>0</v>
       </c>
       <c r="J4" s="6"/>
@@ -5426,27 +5476,27 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <f>'India Rail'!G16</f>
         <v>4658.1263415382473</v>
       </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
         <f>'India Rail'!G15</f>
         <v>2472.3901351241461</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
         <v>0</v>
       </c>
       <c r="J5" s="6"/>
@@ -5455,30 +5505,30 @@
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>'India Road'!$B$47*'India Road'!F47</f>
         <v>33983.37887098475</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <f>'India Road'!$B$47*'India Road'!G47</f>
         <v>139542.31678210635</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <f>'India Road'!$B$47*'India Road'!H47</f>
         <v>0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <f>'India Road'!$B$47*'India Road'!I47+'India Road'!$B$47*'India Road'!K45</f>
         <v>3285391.3043469088</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <f>'India Road'!$B$47*'India Road'!J47</f>
         <v>0</v>
       </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <f>'India Road'!$B$47*'India Road'!L45</f>
         <v>0</v>
       </c>
@@ -5488,35 +5538,53 @@
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <f>'India Road'!$B46*'India Road'!F46</f>
         <v>7236299.1910709729</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <f>'India Road'!$B46*'India Road'!G46</f>
         <v>0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <f>'India Road'!$B46*'India Road'!H46</f>
         <v>236500421.80892903</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>'India Road'!$B46*'India Road'!I46</f>
         <v>0</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <f>'India Road'!$B46*'India Road'!J46</f>
         <v>0</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <f>'India Road'!$B46*'India Road'!K44</f>
         <v>0</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <f>'India Road'!$B46*'India Road'!L44</f>
         <v>0</v>
       </c>
       <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="6"/>
@@ -5533,20 +5601,20 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:8" ht="29">
+      <c r="A1" s="30" t="s">
         <v>89</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -5575,31 +5643,31 @@
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="10">
         <f>'India Road'!$C44*'India Road'!F51</f>
         <v>50841.811388474955</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="10">
         <f>'India Road'!$C44*'India Road'!G51</f>
         <v>197933.03907542647</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="10">
         <f>'India Road'!$C44*'India Road'!H51</f>
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="10">
         <f>'India Road'!$C44*'India Road'!I51</f>
         <v>6580421.1495360993</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="10">
         <f>'India Road'!$C44*'India Road'!J51</f>
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="10">
         <f>'India Road'!$C44*'India Road'!K49</f>
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="10">
         <f>'India Road'!$C44*'India Road'!L49</f>
         <v>0</v>
       </c>
@@ -5608,31 +5676,31 @@
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="10">
         <f>'India Road'!$C45*'India Road'!$F45</f>
         <v>57914.21494034733</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="10">
         <f>'India Road'!$C45*'India Road'!G52</f>
         <v>58432.528398288116</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="10">
         <f>'India Road'!$C45*'India Road'!H52</f>
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="10">
         <f>'India Road'!$C45*'India Road'!I52</f>
         <v>7400632.4716017125</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="10">
         <f>'India Road'!$C45*'India Road'!J52</f>
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="10">
         <f>'India Road'!$C45*'India Road'!K50</f>
         <v>0</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="10">
         <f>'India Road'!$C45*'India Road'!L50</f>
         <v>0</v>
       </c>
@@ -5641,26 +5709,26 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="B4" s="10">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
         <f>'India Aircraft'!B21</f>
-        <v>91.138153526331578</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="74">
-        <v>0</v>
-      </c>
-      <c r="H4">
+        <v>99.163217783158174</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0</v>
+      </c>
+      <c r="G4" s="85">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5668,27 +5736,27 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <f>'India Rail'!G19</f>
         <v>4563.3626425032044</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="C5" s="10">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
         <f>'India Rail'!G18</f>
         <v>1521.1208808344018</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5696,26 +5764,26 @@
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="B6" s="10">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
         <f>'India Ships'!B3</f>
         <v>1200</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5723,31 +5791,31 @@
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <f>'India Road'!$C46*'India Road'!F53</f>
         <v>236864.88584389526</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <f>'India Road'!$C46*'India Road'!G53</f>
         <v>1890078.1983521681</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <f>'India Road'!$C46*'India Road'!H53</f>
         <v>7893763.9158039382</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>'India Road'!$C46*'India Road'!I53</f>
         <v>0</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <f>'India Road'!$C46*'India Road'!J53</f>
         <v>0</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <f>'India Road'!$C46*'India Road'!K51</f>
         <v>0</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <f>'India Road'!$C46*'India Road'!L51</f>
         <v>0</v>
       </c>
@@ -5758,9 +5826,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5908,31 +5979,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC2D0672-FB43-49F4-ADEB-74A315417182}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A23D7061-ABAE-4675-91EC-9841CAAB19FB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{657142FF-FCDE-4CC8-827E-CAAB249CB84E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B6EAEE0-4D4F-49E7-9D11-1D73A6408EFE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC2D0672-FB43-49F4-ADEB-74A315417182}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>